--- a/tame_output/ON/bt/strategyON_20240212.xlsx
+++ b/tame_output/ON/bt/strategyON_20240212.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-02-11</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.0%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,16 +768,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-02-11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.3%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-02-11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.2%</t>
+          <t>-20.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>98.6%</t>
+          <t>98.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-02-11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>93.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-02-11</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>127.6%</t>
+          <t>127.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,16 +1400,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-02-11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>121.2%</t>
+          <t>121.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>0.7%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1870"/>
+  <dimension ref="A1:G1871"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.426779760678667</v>
+        <v>3.424633354969599</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44571,6 +44571,29 @@
       </c>
       <c r="G1870" t="n">
         <v>4.471101886869171</v>
+      </c>
+    </row>
+    <row r="1871">
+      <c r="A1871" s="2" t="n">
+        <v>45333</v>
+      </c>
+      <c r="B1871" t="n">
+        <v>3.420448635964887</v>
+      </c>
+      <c r="C1871" t="n">
+        <v>3.11313585028819</v>
+      </c>
+      <c r="D1871" t="n">
+        <v>1.617495554070377</v>
+      </c>
+      <c r="E1871" t="n">
+        <v>3.759777647602593</v>
+      </c>
+      <c r="F1871" t="n">
+        <v>2.25656622007763</v>
+      </c>
+      <c r="G1871" t="n">
+        <v>4.467075582334768</v>
       </c>
     </row>
   </sheetData>
